--- a/pyfeng/data/ousv_benchmark.xlsx
+++ b/pyfeng/data/ousv_benchmark.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25128"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\PyFENG\pyfeng\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CEF1892-3BDD-4E20-9C62-5502EE9EEC09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D67A6699-EC6A-4FAE-AF24-1E300D54056E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" tabRatio="743" xr2:uid="{CFD8C97F-677E-4081-BE35-9D7DB797B3CD}"/>
+    <workbookView xWindow="20376" yWindow="36" windowWidth="20760" windowHeight="16560" tabRatio="743" xr2:uid="{CFD8C97F-677E-4081-BE35-9D7DB797B3CD}"/>
   </bookViews>
   <sheets>
     <sheet name="Param" sheetId="7" r:id="rId1"/>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="30">
   <si>
     <t>sigma</t>
   </si>
@@ -107,9 +107,6 @@
     <t>Strike</t>
   </si>
   <si>
-    <t>Table 2 in Li and Wu (2019)</t>
-  </si>
-  <si>
     <t>Table 3 in Li and Wu (2019)</t>
   </si>
   <si>
@@ -150,6 +147,15 @@
   </si>
   <si>
     <t>Table 2D/F in Schobel &amp; Zhu (1999)</t>
+  </si>
+  <si>
+    <t>Table 2 in Li and Wu (2019), Table 1 in Choi (2025)</t>
+  </si>
+  <si>
+    <t>Table 2 in Li and Wu (2019), Table 2 in Choi (2025)</t>
+  </si>
+  <si>
+    <t>Table 2 in Li and Wu (2019), Table 3 in Choi (2025)</t>
   </si>
 </sst>
 </file>
@@ -202,11 +208,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -228,9 +233,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -268,7 +273,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -374,7 +379,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -516,7 +521,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -525,13 +530,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0584B610-149E-4DFB-B94E-F604CBCB4976}">
   <dimension ref="A1:K11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="6" max="6" width="6.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="4.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="4.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>7</v>
       </c>
@@ -566,33 +571,33 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="1">
         <v>0.2</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="1">
         <f>B2</f>
         <v>0.2</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="1">
         <v>0.1</v>
       </c>
       <c r="E2" s="2">
         <v>-0.7</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="1">
         <v>4</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="1">
         <v>1</v>
       </c>
-      <c r="H2" s="3">
+      <c r="H2" s="1">
         <v>100</v>
       </c>
-      <c r="I2" s="3">
+      <c r="I2" s="1">
         <v>9.5310000000000006E-2</v>
       </c>
       <c r="J2" s="2" t="str" cm="1">
@@ -600,37 +605,37 @@
         <v>Price</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.35">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <f t="shared" ref="A3:A5" si="0">A2+1</f>
         <v>2</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="1">
         <v>0.2</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="1">
         <f>B3</f>
         <v>0.2</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="1">
         <v>0.1</v>
       </c>
       <c r="E3" s="2">
         <v>-0.7</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="1">
         <v>4</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="1">
         <v>5</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3" s="1">
         <v>100</v>
       </c>
-      <c r="I3" s="3">
+      <c r="I3" s="1">
         <v>9.5310000000000006E-2</v>
       </c>
       <c r="J3" s="2" t="str" cm="1">
@@ -638,37 +643,37 @@
         <v>Price</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.35">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="1">
         <v>0.2</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="1">
         <f>B4</f>
         <v>0.2</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="1">
         <v>0.1</v>
       </c>
       <c r="E4" s="2">
         <v>-0.7</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="1">
         <v>4</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="1">
         <v>10</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="1">
         <v>100</v>
       </c>
-      <c r="I4" s="3">
+      <c r="I4" s="1">
         <v>9.5310000000000006E-2</v>
       </c>
       <c r="J4" s="2" t="str" cm="1">
@@ -676,253 +681,253 @@
         <v>Price</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="1">
         <v>0.25</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="1">
         <v>0.25</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="1">
         <v>0.3</v>
       </c>
       <c r="E5" s="2">
         <v>-0.6</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="1">
         <v>8</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="1">
         <v>1</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="1">
         <v>100</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5" s="1">
         <v>9.5310000000000006E-2</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>11</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.35">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="1">
         <v>0.2</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="1">
         <v>0.2</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="1">
         <v>0.1</v>
       </c>
       <c r="E6" s="2">
         <v>0</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="1">
         <v>4</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="1">
         <v>0.5</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6" s="1">
         <v>100</v>
       </c>
-      <c r="I6" s="3">
+      <c r="I6" s="1">
         <v>9.5299999999999996E-2</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>11</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="1">
         <v>0.2</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="1">
         <v>0.1</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="1">
         <v>0.1</v>
       </c>
       <c r="E7" s="2">
         <v>0</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="1">
         <v>4</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7" s="1">
         <v>0.5</v>
       </c>
-      <c r="H7" s="3">
+      <c r="H7" s="1">
         <v>100</v>
       </c>
-      <c r="I7" s="3">
+      <c r="I7" s="1">
         <v>9.5299999999999996E-2</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>11</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="1">
         <v>0.2</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="1">
         <v>0.3</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="1">
         <v>0.1</v>
       </c>
       <c r="E8" s="2">
         <v>0</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="1">
         <v>4</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8" s="1">
         <v>0.5</v>
       </c>
-      <c r="H8" s="3">
+      <c r="H8" s="1">
         <v>100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="I8" s="1">
         <v>9.5299999999999996E-2</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>11</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="1">
         <v>0.15</v>
       </c>
       <c r="C9" s="2">
         <v>0</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="1">
         <v>0.1</v>
       </c>
       <c r="E9" s="2">
         <v>0.5</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="1">
         <v>4</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9" s="1">
         <v>0.5</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9" s="1">
         <v>100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="I9" s="1">
         <v>9.5299999999999996E-2</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>11</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="1">
         <v>0.15</v>
       </c>
       <c r="C10" s="2">
         <v>0</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="1">
         <v>0.1</v>
       </c>
       <c r="E10" s="2">
         <v>0</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="1">
         <v>4</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10" s="1">
         <v>0.5</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H10" s="1">
         <v>100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="I10" s="1">
         <v>9.5299999999999996E-2</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>11</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.35">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="1">
         <v>0.15</v>
       </c>
       <c r="C11" s="2">
         <v>0</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="1">
         <v>0.1</v>
       </c>
       <c r="E11" s="2">
         <v>-0.5</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="1">
         <v>4</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11" s="1">
         <v>0.5</v>
       </c>
-      <c r="H11" s="3">
+      <c r="H11" s="1">
         <v>100</v>
       </c>
-      <c r="I11" s="3">
+      <c r="I11" s="1">
         <v>9.5299999999999996E-2</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>11</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -934,19 +939,19 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DAD2039-CD05-46C6-AAEA-DBB61BC6455E}">
   <dimension ref="A1:J8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="3" width="8.7265625" style="6"/>
+    <col min="2" max="3" width="8.77734375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="6">
+      <c r="C1" s="5">
         <v>0</v>
       </c>
       <c r="D1">
@@ -959,27 +964,27 @@
         <v>0.3</v>
       </c>
       <c r="G1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" t="s">
         <v>23</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>24</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>25</v>
       </c>
-      <c r="J1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>90</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="5">
         <f>C2</f>
         <v>14.2</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="5">
         <v>14.2</v>
       </c>
       <c r="D2">
@@ -1004,15 +1009,15 @@
         <v>15.757</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>95</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="5">
         <f t="shared" ref="B3:B8" si="0">C3</f>
         <v>9.5269999999999992</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="5">
         <v>9.5269999999999992</v>
       </c>
       <c r="D3">
@@ -1037,15 +1042,15 @@
         <v>12.212999999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>100</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="5">
         <f t="shared" si="0"/>
         <v>5.2690000000000001</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="5">
         <v>5.2690000000000001</v>
       </c>
       <c r="D4">
@@ -1070,15 +1075,15 @@
         <v>9.1869999999999994</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>105</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="5">
         <f t="shared" si="0"/>
         <v>2.17</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="5">
         <v>2.17</v>
       </c>
       <c r="D5">
@@ -1103,15 +1108,15 @@
         <v>6.7069999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>110</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="5">
         <f t="shared" si="0"/>
         <v>0.64500000000000002</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="5">
         <v>0.64500000000000002</v>
       </c>
       <c r="D6">
@@ -1136,15 +1141,15 @@
         <v>4.7549999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>115</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="5">
         <f t="shared" si="0"/>
         <v>0.15</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="5">
         <v>0.15</v>
       </c>
       <c r="D7">
@@ -1169,15 +1174,15 @@
         <v>3.278</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>120</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="5">
         <f t="shared" si="0"/>
         <v>0.03</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="5">
         <v>0.03</v>
       </c>
       <c r="D8">
@@ -1210,19 +1215,19 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF4B277F-7813-4B15-B237-E2A8BB879385}">
   <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="3" width="8.7265625" style="6"/>
+    <col min="2" max="3" width="8.77734375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="6">
+      <c r="C1" s="5">
         <v>0</v>
       </c>
       <c r="D1">
@@ -1235,15 +1240,15 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>90</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="5">
         <f>C2</f>
         <v>14.225</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="5">
         <v>14.225</v>
       </c>
       <c r="D2">
@@ -1256,15 +1261,15 @@
         <v>15.887</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>95</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="5">
         <f t="shared" ref="B3:B8" si="0">C3</f>
         <v>9.6</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="5">
         <v>9.6</v>
       </c>
       <c r="D3">
@@ -1277,15 +1282,15 @@
         <v>12.305999999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>100</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="5">
         <f t="shared" si="0"/>
         <v>5.3719999999999999</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="5">
         <v>5.3719999999999999</v>
       </c>
       <c r="D4">
@@ -1298,15 +1303,15 @@
         <v>9.2129999999999992</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>105</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="5">
         <f t="shared" si="0"/>
         <v>2.1520000000000001</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="5">
         <v>2.1520000000000001</v>
       </c>
       <c r="D5">
@@ -1319,15 +1324,15 @@
         <v>6.6520000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>110</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="5">
         <f t="shared" si="0"/>
         <v>0.504</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="5">
         <v>0.504</v>
       </c>
       <c r="D6">
@@ -1340,15 +1345,15 @@
         <v>4.6260000000000003</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>115</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="5">
         <f t="shared" si="0"/>
         <v>6.0999999999999999E-2</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="5">
         <v>6.0999999999999999E-2</v>
       </c>
       <c r="D7">
@@ -1361,15 +1366,15 @@
         <v>3.097</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>120</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="5">
         <f t="shared" si="0"/>
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="5">
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="D8">
@@ -1390,13 +1395,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5761A8C7-5DBE-4514-94EE-A5933B58C928}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="10.90625" customWidth="1"/>
-    <col min="3" max="3" width="9.6328125" customWidth="1"/>
+    <col min="2" max="2" width="10.88671875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>12</v>
       </c>
@@ -1404,17 +1409,17 @@
         <v>11</v>
       </c>
       <c r="C1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>100</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="4">
         <v>13.214919999999999</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="3">
         <v>13.214930000000001</v>
       </c>
     </row>
@@ -1426,13 +1431,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62FCD568-C350-4F53-ADA8-3A672B89280F}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="10.90625" customWidth="1"/>
-    <col min="3" max="3" width="9.6328125" customWidth="1"/>
+    <col min="2" max="2" width="10.88671875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>12</v>
       </c>
@@ -1440,17 +1445,17 @@
         <v>11</v>
       </c>
       <c r="C1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>100</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="4">
         <v>40.797688999999998</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="3">
         <v>40.797730000000001</v>
       </c>
     </row>
@@ -1462,13 +1467,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0F9FDE4-4755-4E32-814A-85CBF4499A47}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="10.90625" customWidth="1"/>
-    <col min="3" max="3" width="9.6328125" customWidth="1"/>
+    <col min="2" max="2" width="10.88671875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>12</v>
       </c>
@@ -1476,17 +1481,17 @@
         <v>11</v>
       </c>
       <c r="C1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>100</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="4">
         <v>62.763120000000001</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="3">
         <v>62.763120000000001</v>
       </c>
     </row>
@@ -1498,13 +1503,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{061D7AAA-9DDC-4D37-BE68-08E1503EF93E}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="10.90625" customWidth="1"/>
-    <col min="3" max="3" width="9.6328125" customWidth="1"/>
+    <col min="2" max="2" width="10.88671875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>12</v>
       </c>
@@ -1512,36 +1517,36 @@
         <v>11</v>
       </c>
       <c r="C1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>90</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="4">
         <v>21.418717000000001</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="3">
         <v>21.41873</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>100</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="4">
         <v>15.16797</v>
       </c>
       <c r="C3">
         <v>15.16798</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>110</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="4">
         <v>10.174469</v>
       </c>
       <c r="C4">
@@ -1556,24 +1561,24 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D6B2DAA-FB44-4708-96F6-DD88B104329D}">
   <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="8.7265625" style="6"/>
-    <col min="9" max="9" width="8.7265625" style="6"/>
+    <col min="2" max="2" width="8.77734375" style="5"/>
+    <col min="9" max="9" width="8.77734375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" t="s">
         <v>16</v>
-      </c>
-      <c r="D1" t="s">
-        <v>17</v>
       </c>
       <c r="E1">
         <v>-1</v>
@@ -1587,7 +1592,7 @@
       <c r="H1">
         <v>-0.25</v>
       </c>
-      <c r="I1" s="6">
+      <c r="I1" s="5">
         <v>0</v>
       </c>
       <c r="J1">
@@ -1603,11 +1608,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>90</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="5">
         <f>I2</f>
         <v>15.154999999999999</v>
       </c>
@@ -1629,7 +1634,7 @@
       <c r="H2">
         <v>15.225</v>
       </c>
-      <c r="I2" s="6">
+      <c r="I2" s="5">
         <v>15.154999999999999</v>
       </c>
       <c r="J2">
@@ -1645,11 +1650,11 @@
         <v>14.827999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>95</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="5">
         <f t="shared" ref="B3:B8" si="0">I3</f>
         <v>11.379</v>
       </c>
@@ -1671,7 +1676,7 @@
       <c r="H3">
         <v>11.443</v>
       </c>
-      <c r="I3" s="6">
+      <c r="I3" s="5">
         <v>11.379</v>
       </c>
       <c r="J3">
@@ -1687,11 +1692,11 @@
         <v>11.092000000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>100</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="5">
         <f t="shared" si="0"/>
         <v>8.1760000000000002</v>
       </c>
@@ -1713,7 +1718,7 @@
       <c r="H4">
         <v>8.2100000000000009</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="5">
         <v>8.1760000000000002</v>
       </c>
       <c r="J4">
@@ -1729,11 +1734,11 @@
         <v>8.0340000000000007</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>105</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="5">
         <f t="shared" si="0"/>
         <v>5.617</v>
       </c>
@@ -1755,7 +1760,7 @@
       <c r="H5">
         <v>5.6059999999999999</v>
       </c>
-      <c r="I5" s="6">
+      <c r="I5" s="5">
         <v>5.617</v>
       </c>
       <c r="J5">
@@ -1771,11 +1776,11 @@
         <v>5.665</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>110</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="5">
         <f t="shared" si="0"/>
         <v>3.694</v>
       </c>
@@ -1797,7 +1802,7 @@
       <c r="H6">
         <v>3.6379999999999999</v>
       </c>
-      <c r="I6" s="6">
+      <c r="I6" s="5">
         <v>3.694</v>
       </c>
       <c r="J6">
@@ -1813,11 +1818,11 @@
         <v>3.9089999999999998</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>115</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="5">
         <f t="shared" si="0"/>
         <v>2.3330000000000002</v>
       </c>
@@ -1839,7 +1844,7 @@
       <c r="H7">
         <v>2.246</v>
       </c>
-      <c r="I7" s="6">
+      <c r="I7" s="5">
         <v>2.3330000000000002</v>
       </c>
       <c r="J7">
@@ -1855,11 +1860,11 @@
         <v>2.653</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>120</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="5">
         <f t="shared" si="0"/>
         <v>1.42</v>
       </c>
@@ -1881,7 +1886,7 @@
       <c r="H8">
         <v>1.321</v>
       </c>
-      <c r="I8" s="6">
+      <c r="I8" s="5">
         <v>1.42</v>
       </c>
       <c r="J8">
@@ -1905,21 +1910,21 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AE24A2D-D7B0-4647-B24E-987FE01149C0}">
   <dimension ref="A1:L8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="8.7265625" style="6"/>
-    <col min="8" max="8" width="8.7265625" style="6"/>
+    <col min="2" max="2" width="8.77734375" style="5"/>
+    <col min="8" max="8" width="8.77734375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D1">
         <v>-1</v>
@@ -1933,7 +1938,7 @@
       <c r="G1">
         <v>-0.25</v>
       </c>
-      <c r="H1" s="6">
+      <c r="H1" s="5">
         <v>0</v>
       </c>
       <c r="I1">
@@ -1949,11 +1954,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>90</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="5">
         <f>H2</f>
         <v>14.515000000000001</v>
       </c>
@@ -1972,7 +1977,7 @@
       <c r="G2">
         <v>14.571999999999999</v>
       </c>
-      <c r="H2" s="6">
+      <c r="H2" s="5">
         <v>14.515000000000001</v>
       </c>
       <c r="I2">
@@ -1988,11 +1993,11 @@
         <v>14.260999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>95</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="5">
         <f t="shared" ref="B3:B8" si="0">H3</f>
         <v>10.346</v>
       </c>
@@ -2011,7 +2016,7 @@
       <c r="G3">
         <v>10.414999999999999</v>
       </c>
-      <c r="H3" s="6">
+      <c r="H3" s="5">
         <v>10.346</v>
       </c>
       <c r="I3">
@@ -2027,11 +2032,11 @@
         <v>10.005000000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>100</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="5">
         <f t="shared" si="0"/>
         <v>6.8029999999999999</v>
       </c>
@@ -2050,7 +2055,7 @@
       <c r="G4">
         <v>6.8490000000000002</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="5">
         <v>6.8029999999999999</v>
       </c>
       <c r="I4">
@@ -2066,11 +2071,11 @@
         <v>6.5869999999999997</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>105</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="5">
         <f t="shared" si="0"/>
         <v>4.093</v>
       </c>
@@ -2089,7 +2094,7 @@
       <c r="G5">
         <v>4.085</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="5">
         <v>4.093</v>
       </c>
       <c r="I5">
@@ -2105,11 +2110,11 @@
         <v>4.125</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>110</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="5">
         <f t="shared" si="0"/>
         <v>2.254</v>
       </c>
@@ -2128,7 +2133,7 @@
       <c r="G6">
         <v>2.1890000000000001</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="5">
         <v>2.254</v>
       </c>
       <c r="I6">
@@ -2144,11 +2149,11 @@
         <v>2.4889999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>115</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="5">
         <f t="shared" si="0"/>
         <v>1.1439999999999999</v>
       </c>
@@ -2167,7 +2172,7 @@
       <c r="G7">
         <v>1.0529999999999999</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="5">
         <v>1.1439999999999999</v>
       </c>
       <c r="I7">
@@ -2183,11 +2188,11 @@
         <v>1.4630000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>120</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="5">
         <f t="shared" si="0"/>
         <v>0.54200000000000004</v>
       </c>
@@ -2206,7 +2211,7 @@
       <c r="G8">
         <v>0.45800000000000002</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="5">
         <v>0.54200000000000004</v>
       </c>
       <c r="I8">
@@ -2230,21 +2235,21 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8F9FD47-1490-4478-A2C0-1F2C85519101}">
   <dimension ref="A1:L8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="8.7265625" style="6"/>
-    <col min="8" max="8" width="8.7265625" style="6"/>
+    <col min="2" max="2" width="8.77734375" style="5"/>
+    <col min="8" max="8" width="8.77734375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D1">
         <v>-1</v>
@@ -2258,7 +2263,7 @@
       <c r="G1">
         <v>-0.25</v>
       </c>
-      <c r="H1" s="6">
+      <c r="H1" s="5">
         <v>0</v>
       </c>
       <c r="I1">
@@ -2274,11 +2279,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>90</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="5">
         <f>H2</f>
         <v>16.106000000000002</v>
       </c>
@@ -2297,7 +2302,7 @@
       <c r="G2">
         <v>16.172000000000001</v>
       </c>
-      <c r="H2" s="6">
+      <c r="H2" s="5">
         <v>16.106000000000002</v>
       </c>
       <c r="I2">
@@ -2313,11 +2318,11 @@
         <v>15.81</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>95</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="5">
         <f t="shared" ref="B3:B8" si="0">H3</f>
         <v>12.651</v>
       </c>
@@ -2336,7 +2341,7 @@
       <c r="G3">
         <v>12.702</v>
       </c>
-      <c r="H3" s="6">
+      <c r="H3" s="5">
         <v>12.651</v>
       </c>
       <c r="I3">
@@ -2352,11 +2357,11 @@
         <v>12.432</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>100</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="5">
         <f t="shared" si="0"/>
         <v>9.6869999999999994</v>
       </c>
@@ -2375,7 +2380,7 @@
       <c r="G4">
         <v>9.7100000000000009</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="5">
         <v>9.6869999999999994</v>
       </c>
       <c r="I4">
@@ -2391,11 +2396,11 @@
         <v>9.5980000000000008</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>105</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="5">
         <f t="shared" si="0"/>
         <v>7.2370000000000001</v>
       </c>
@@ -2414,7 +2419,7 @@
       <c r="G5">
         <v>7.2229999999999999</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="5">
         <v>7.2370000000000001</v>
       </c>
       <c r="I5">
@@ -2430,11 +2435,11 @@
         <v>7.2960000000000003</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>110</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="5">
         <f t="shared" si="0"/>
         <v>5.2789999999999999</v>
       </c>
@@ -2453,7 +2458,7 @@
       <c r="G6">
         <v>5.23</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="5">
         <v>5.2789999999999999</v>
       </c>
       <c r="I6">
@@ -2469,11 +2474,11 @@
         <v>5.4749999999999996</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>115</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="5">
         <f t="shared" si="0"/>
         <v>3.7679999999999998</v>
       </c>
@@ -2492,7 +2497,7 @@
       <c r="G7">
         <v>3.69</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="5">
         <v>3.7679999999999998</v>
       </c>
       <c r="I7">
@@ -2508,11 +2513,11 @@
         <v>4.0650000000000004</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>120</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="5">
         <f t="shared" si="0"/>
         <v>2.6349999999999998</v>
       </c>
@@ -2531,7 +2536,7 @@
       <c r="G8">
         <v>2.54</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="5">
         <v>2.6349999999999998</v>
       </c>
       <c r="I8">
@@ -2555,19 +2560,19 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DDE6EBC-20C5-4C4A-8F41-F3804F8029F0}">
   <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="3" width="8.7265625" style="6"/>
+    <col min="2" max="3" width="8.77734375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="6">
+      <c r="C1" s="5">
         <v>0</v>
       </c>
       <c r="D1">
@@ -2580,15 +2585,15 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>90</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="5">
         <f>C2</f>
         <v>14.189</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="5">
         <v>14.189</v>
       </c>
       <c r="D2">
@@ -2601,15 +2606,15 @@
         <v>15.608000000000001</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>95</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="5">
         <f t="shared" ref="B3:B8" si="0">C3</f>
         <v>9.4589999999999996</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="5">
         <v>9.4589999999999996</v>
       </c>
       <c r="D3">
@@ -2622,15 +2627,15 @@
         <v>12.082000000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>100</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="5">
         <f t="shared" si="0"/>
         <v>5.141</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="5">
         <v>5.141</v>
       </c>
       <c r="D4">
@@ -2643,15 +2648,15 @@
         <v>9.109</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>105</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="5">
         <f t="shared" si="0"/>
         <v>2.173</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="5">
         <v>2.173</v>
       </c>
       <c r="D5">
@@ -2664,15 +2669,15 @@
         <v>6.7030000000000003</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>110</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="5">
         <f t="shared" si="0"/>
         <v>0.76300000000000001</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="5">
         <v>0.76300000000000001</v>
       </c>
       <c r="D6">
@@ -2685,15 +2690,15 @@
         <v>4.8280000000000003</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>115</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="5">
         <f t="shared" si="0"/>
         <v>0.24399999999999999</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="5">
         <v>0.24399999999999999</v>
       </c>
       <c r="D7">
@@ -2706,15 +2711,15 @@
         <v>3.4140000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>120</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="5">
         <f t="shared" si="0"/>
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="5">
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="D8">
